--- a/Assets/Data/Tables/Stage.xlsx
+++ b/Assets/Data/Tables/Stage.xlsx
@@ -626,7 +626,7 @@
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>체력 계수. 버섯 체력 × 이 값, 보스 체력 = 100 × 보스 hpRate × 이 값</t>
+          <t>체력 계수. 버섯 체력 × 이 값, 보스 체력 = 100 × 보스 hpRate × 이 값. 그 스테이지 시점의 공격력을 따라감</t>
         </is>
       </c>
       <c r="G3" s="4" t="inlineStr">
@@ -688,7 +688,7 @@
       <c r="J4" s="5" t="n"/>
       <c r="K4" s="5" t="inlineStr">
         <is>
-          <t>예상 도달 0.0분</t>
+          <t>2026-10-26 밸런스: 체력 계수 = 그 스테이지 시점 공격력(봇 실측)을 다듬은 값, 보상 배율 = 구간별 판당 수입 배율 목표(1~6 ×1.5, 7~11 ×1.35, 12~31 ×1.25, 32~46 ×1.15, 47~50 ×1.12)</t>
         </is>
       </c>
     </row>
@@ -715,17 +715,17 @@
         </is>
       </c>
       <c r="F5" s="5" t="n">
-        <v>1.019</v>
+        <v>1.201</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>1.019</v>
+        <v>1.286</v>
       </c>
       <c r="H5" s="5" t="n"/>
       <c r="I5" s="5" t="n"/>
       <c r="J5" s="5" t="n"/>
       <c r="K5" s="5" t="inlineStr">
         <is>
-          <t>예상 도달 0.5분</t>
+          <t>2026-10-26 밸런스: 체력 계수 = 그 스테이지 시점 공격력(봇 실측)을 다듬은 값, 보상 배율 = 구간별 판당 수입 배율 목표(1~6 ×1.5, 7~11 ×1.35, 12~31 ×1.25, 32~46 ×1.15, 47~50 ×1.12)</t>
         </is>
       </c>
     </row>
@@ -752,17 +752,17 @@
         </is>
       </c>
       <c r="F6" s="5" t="n">
-        <v>1.039</v>
+        <v>1.34</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>1.039</v>
+        <v>1.535</v>
       </c>
       <c r="H6" s="5" t="n"/>
       <c r="I6" s="5" t="n"/>
       <c r="J6" s="5" t="n"/>
       <c r="K6" s="5" t="inlineStr">
         <is>
-          <t>예상 도달 1.0분</t>
+          <t>2026-10-26 밸런스: 체력 계수 = 그 스테이지 시점 공격력(봇 실측)을 다듬은 값, 보상 배율 = 구간별 판당 수입 배율 목표(1~6 ×1.5, 7~11 ×1.35, 12~31 ×1.25, 32~46 ×1.15, 47~50 ×1.12)</t>
         </is>
       </c>
     </row>
@@ -789,17 +789,17 @@
         </is>
       </c>
       <c r="F7" s="5" t="n">
-        <v>1.059</v>
+        <v>1.67</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>1.059</v>
+        <v>2.048</v>
       </c>
       <c r="H7" s="5" t="n"/>
       <c r="I7" s="5" t="n"/>
       <c r="J7" s="5" t="n"/>
       <c r="K7" s="5" t="inlineStr">
         <is>
-          <t>예상 도달 1.5분</t>
+          <t>2026-10-26 밸런스: 체력 계수 = 그 스테이지 시점 공격력(봇 실측)을 다듬은 값, 보상 배율 = 구간별 판당 수입 배율 목표(1~6 ×1.5, 7~11 ×1.35, 12~31 ×1.25, 32~46 ×1.15, 47~50 ×1.12)</t>
         </is>
       </c>
     </row>
@@ -826,17 +826,17 @@
         </is>
       </c>
       <c r="F8" s="5" t="n">
-        <v>1.08</v>
+        <v>2.304</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>1.08</v>
+        <v>3.024</v>
       </c>
       <c r="H8" s="5" t="n"/>
       <c r="I8" s="5" t="n"/>
       <c r="J8" s="5" t="n"/>
       <c r="K8" s="5" t="inlineStr">
         <is>
-          <t>예상 도달 2.0분</t>
+          <t>2026-10-26 밸런스: 체력 계수 = 그 스테이지 시점 공격력(봇 실측)을 다듬은 값, 보상 배율 = 구간별 판당 수입 배율 목표(1~6 ×1.5, 7~11 ×1.35, 12~31 ×1.25, 32~46 ×1.15, 47~50 ×1.12)</t>
         </is>
       </c>
     </row>
@@ -863,17 +863,17 @@
         </is>
       </c>
       <c r="F9" s="5" t="n">
-        <v>1.101</v>
+        <v>2.552</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>1.101</v>
+        <v>3.586</v>
       </c>
       <c r="H9" s="5" t="n"/>
       <c r="I9" s="5" t="n"/>
       <c r="J9" s="5" t="n"/>
       <c r="K9" s="5" t="inlineStr">
         <is>
-          <t>예상 도달 2.5분</t>
+          <t>2026-10-26 밸런스: 체력 계수 = 그 스테이지 시점 공격력(봇 실측)을 다듬은 값, 보상 배율 = 구간별 판당 수입 배율 목표(1~6 ×1.5, 7~11 ×1.35, 12~31 ×1.25, 32~46 ×1.15, 47~50 ×1.12)</t>
         </is>
       </c>
     </row>
@@ -900,17 +900,17 @@
         </is>
       </c>
       <c r="F10" s="5" t="n">
-        <v>1.122</v>
+        <v>2.826</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>1.122</v>
+        <v>3.928</v>
       </c>
       <c r="H10" s="5" t="n"/>
       <c r="I10" s="5" t="n"/>
       <c r="J10" s="5" t="n"/>
       <c r="K10" s="5" t="inlineStr">
         <is>
-          <t>예상 도달 3.0분</t>
+          <t>2026-10-26 밸런스: 체력 계수 = 그 스테이지 시점 공격력(봇 실측)을 다듬은 값, 보상 배율 = 구간별 판당 수입 배율 목표(1~6 ×1.5, 7~11 ×1.35, 12~31 ×1.25, 32~46 ×1.15, 47~50 ×1.12)</t>
         </is>
       </c>
     </row>
@@ -937,17 +937,17 @@
         </is>
       </c>
       <c r="F11" s="5" t="n">
-        <v>1.144</v>
+        <v>3.13</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>1.144</v>
+        <v>4.306</v>
       </c>
       <c r="H11" s="5" t="n"/>
       <c r="I11" s="5" t="n"/>
       <c r="J11" s="5" t="n"/>
       <c r="K11" s="5" t="inlineStr">
         <is>
-          <t>예상 도달 3.5분</t>
+          <t>2026-10-26 밸런스: 체력 계수 = 그 스테이지 시점 공격력(봇 실측)을 다듬은 값, 보상 배율 = 구간별 판당 수입 배율 목표(1~6 ×1.5, 7~11 ×1.35, 12~31 ×1.25, 32~46 ×1.15, 47~50 ×1.12)</t>
         </is>
       </c>
     </row>
@@ -974,17 +974,17 @@
         </is>
       </c>
       <c r="F12" s="5" t="n">
-        <v>1.167</v>
+        <v>3.708</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>1.167</v>
+        <v>5.048</v>
       </c>
       <c r="H12" s="5" t="n"/>
       <c r="I12" s="5" t="n"/>
       <c r="J12" s="5" t="n"/>
       <c r="K12" s="5" t="inlineStr">
         <is>
-          <t>예상 도달 4.0분</t>
+          <t>2026-10-26 밸런스: 체력 계수 = 그 스테이지 시점 공격력(봇 실측)을 다듬은 값, 보상 배율 = 구간별 판당 수입 배율 목표(1~6 ×1.5, 7~11 ×1.35, 12~31 ×1.25, 32~46 ×1.15, 47~50 ×1.12)</t>
         </is>
       </c>
     </row>
@@ -1011,10 +1011,10 @@
         </is>
       </c>
       <c r="F13" s="6" t="n">
-        <v>1.189</v>
+        <v>3.966</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>1.189</v>
+        <v>5.344</v>
       </c>
       <c r="H13" s="6" t="n">
         <v>6001</v>
@@ -1023,7 +1023,7 @@
       <c r="J13" s="6" t="n"/>
       <c r="K13" s="6" t="inlineStr">
         <is>
-          <t>예상 도달 4.5분 · 보스 처치 목표 10분</t>
+          <t>2026-10-26 밸런스: 체력 계수 = 그 스테이지 시점 공격력(봇 실측)을 다듬은 값, 보상 배율 = 구간별 판당 수입 배율 목표(1~6 ×1.5, 7~11 ×1.35, 12~31 ×1.25, 32~46 ×1.15, 47~50 ×1.12)</t>
         </is>
       </c>
     </row>
@@ -1050,17 +1050,17 @@
         </is>
       </c>
       <c r="F14" s="5" t="n">
-        <v>1.47</v>
+        <v>4.242</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>1.47</v>
+        <v>5.655</v>
       </c>
       <c r="H14" s="5" t="n"/>
       <c r="I14" s="5" t="n"/>
       <c r="J14" s="5" t="n"/>
       <c r="K14" s="5" t="inlineStr">
         <is>
-          <t>예상 도달 10.0분</t>
+          <t>2026-10-26 밸런스: 체력 계수 = 그 스테이지 시점 공격력(봇 실측)을 다듬은 값, 보상 배율 = 구간별 판당 수입 배율 목표(1~6 ×1.5, 7~11 ×1.35, 12~31 ×1.25, 32~46 ×1.15, 47~50 ×1.12)</t>
         </is>
       </c>
     </row>
@@ -1087,17 +1087,17 @@
         </is>
       </c>
       <c r="F15" s="5" t="n">
-        <v>1.498</v>
+        <v>4.538</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>1.498</v>
+        <v>7.236</v>
       </c>
       <c r="H15" s="5" t="n"/>
       <c r="I15" s="5" t="n"/>
       <c r="J15" s="5" t="n"/>
       <c r="K15" s="5" t="inlineStr">
         <is>
-          <t>예상 도달 10.5분</t>
+          <t>2026-10-26 밸런스: 체력 계수 = 그 스테이지 시점 공격력(봇 실측)을 다듬은 값, 보상 배율 = 구간별 판당 수입 배율 목표(1~6 ×1.5, 7~11 ×1.35, 12~31 ×1.25, 32~46 ×1.15, 47~50 ×1.12)</t>
         </is>
       </c>
     </row>
@@ -1124,17 +1124,17 @@
         </is>
       </c>
       <c r="F16" s="5" t="n">
-        <v>1.527</v>
+        <v>4.854</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>1.527</v>
+        <v>9.256</v>
       </c>
       <c r="H16" s="5" t="n"/>
       <c r="I16" s="5" t="n"/>
       <c r="J16" s="5" t="n"/>
       <c r="K16" s="5" t="inlineStr">
         <is>
-          <t>예상 도달 11.0분</t>
+          <t>2026-10-26 밸런스: 체력 계수 = 그 스테이지 시점 공격력(봇 실측)을 다듬은 값, 보상 배율 = 구간별 판당 수입 배율 목표(1~6 ×1.5, 7~11 ×1.35, 12~31 ×1.25, 32~46 ×1.15, 47~50 ×1.12)</t>
         </is>
       </c>
     </row>
@@ -1161,17 +1161,17 @@
         </is>
       </c>
       <c r="F17" s="5" t="n">
-        <v>1.557</v>
+        <v>4.854</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>1.557</v>
+        <v>11.07</v>
       </c>
       <c r="H17" s="5" t="n"/>
       <c r="I17" s="5" t="n"/>
       <c r="J17" s="5" t="n"/>
       <c r="K17" s="5" t="inlineStr">
         <is>
-          <t>예상 도달 11.5분</t>
+          <t>2026-10-26 밸런스: 체력 계수 = 그 스테이지 시점 공격력(봇 실측)을 다듬은 값, 보상 배율 = 구간별 판당 수입 배율 목표(1~6 ×1.5, 7~11 ×1.35, 12~31 ×1.25, 32~46 ×1.15, 47~50 ×1.12)</t>
         </is>
       </c>
     </row>
@@ -1198,17 +1198,17 @@
         </is>
       </c>
       <c r="F18" s="5" t="n">
-        <v>1.587</v>
+        <v>4.854</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>1.587</v>
+        <v>13.238</v>
       </c>
       <c r="H18" s="5" t="n"/>
       <c r="I18" s="5" t="n"/>
       <c r="J18" s="5" t="n"/>
       <c r="K18" s="5" t="inlineStr">
         <is>
-          <t>예상 도달 12.0분</t>
+          <t>2026-10-26 밸런스: 체력 계수 = 그 스테이지 시점 공격력(봇 실측)을 다듬은 값, 보상 배율 = 구간별 판당 수입 배율 목표(1~6 ×1.5, 7~11 ×1.35, 12~31 ×1.25, 32~46 ×1.15, 47~50 ×1.12)</t>
         </is>
       </c>
     </row>
@@ -1235,17 +1235,17 @@
         </is>
       </c>
       <c r="F19" s="5" t="n">
-        <v>1.618</v>
+        <v>4.854</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>1.618</v>
+        <v>15.832</v>
       </c>
       <c r="H19" s="5" t="n"/>
       <c r="I19" s="5" t="n"/>
       <c r="J19" s="5" t="n"/>
       <c r="K19" s="5" t="inlineStr">
         <is>
-          <t>예상 도달 12.5분</t>
+          <t>2026-10-26 밸런스: 체력 계수 = 그 스테이지 시점 공격력(봇 실측)을 다듬은 값, 보상 배율 = 구간별 판당 수입 배율 목표(1~6 ×1.5, 7~11 ×1.35, 12~31 ×1.25, 32~46 ×1.15, 47~50 ×1.12)</t>
         </is>
       </c>
     </row>
@@ -1272,17 +1272,17 @@
         </is>
       </c>
       <c r="F20" s="5" t="n">
-        <v>1.65</v>
+        <v>4.854</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>1.65</v>
+        <v>18.932</v>
       </c>
       <c r="H20" s="5" t="n"/>
       <c r="I20" s="5" t="n"/>
       <c r="J20" s="5" t="n"/>
       <c r="K20" s="5" t="inlineStr">
         <is>
-          <t>예상 도달 13.0분</t>
+          <t>2026-10-26 밸런스: 체력 계수 = 그 스테이지 시점 공격력(봇 실측)을 다듬은 값, 보상 배율 = 구간별 판당 수입 배율 목표(1~6 ×1.5, 7~11 ×1.35, 12~31 ×1.25, 32~46 ×1.15, 47~50 ×1.12)</t>
         </is>
       </c>
     </row>
@@ -1309,17 +1309,17 @@
         </is>
       </c>
       <c r="F21" s="5" t="n">
-        <v>1.682</v>
+        <v>4.854</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>1.682</v>
+        <v>22.642</v>
       </c>
       <c r="H21" s="5" t="n"/>
       <c r="I21" s="5" t="n"/>
       <c r="J21" s="5" t="n"/>
       <c r="K21" s="5" t="inlineStr">
         <is>
-          <t>예상 도달 13.5분</t>
+          <t>2026-10-26 밸런스: 체력 계수 = 그 스테이지 시점 공격력(봇 실측)을 다듬은 값, 보상 배율 = 구간별 판당 수입 배율 목표(1~6 ×1.5, 7~11 ×1.35, 12~31 ×1.25, 32~46 ×1.15, 47~50 ×1.12)</t>
         </is>
       </c>
     </row>
@@ -1346,17 +1346,17 @@
         </is>
       </c>
       <c r="F22" s="5" t="n">
-        <v>1.714</v>
+        <v>4.854</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>1.714</v>
+        <v>27.076</v>
       </c>
       <c r="H22" s="5" t="n"/>
       <c r="I22" s="5" t="n"/>
       <c r="J22" s="5" t="n"/>
       <c r="K22" s="5" t="inlineStr">
         <is>
-          <t>예상 도달 14.0분</t>
+          <t>2026-10-26 밸런스: 체력 계수 = 그 스테이지 시점 공격력(봇 실측)을 다듬은 값, 보상 배율 = 구간별 판당 수입 배율 목표(1~6 ×1.5, 7~11 ×1.35, 12~31 ×1.25, 32~46 ×1.15, 47~50 ×1.12)</t>
         </is>
       </c>
     </row>
@@ -1383,10 +1383,10 @@
         </is>
       </c>
       <c r="F23" s="6" t="n">
-        <v>1.748</v>
+        <v>4.854</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>1.748</v>
+        <v>32.382</v>
       </c>
       <c r="H23" s="6" t="n">
         <v>6002</v>
@@ -1395,7 +1395,7 @@
       <c r="J23" s="6" t="n"/>
       <c r="K23" s="6" t="inlineStr">
         <is>
-          <t>예상 도달 14.5분 · 보스 처치 목표 25분</t>
+          <t>2026-10-26 밸런스: 체력 계수 = 그 스테이지 시점 공격력(봇 실측)을 다듬은 값, 보상 배율 = 구간별 판당 수입 배율 목표(1~6 ×1.5, 7~11 ×1.35, 12~31 ×1.25, 32~46 ×1.15, 47~50 ×1.12)</t>
         </is>
       </c>
     </row>
@@ -1422,17 +1422,17 @@
         </is>
       </c>
       <c r="F24" s="5" t="n">
-        <v>2.619</v>
+        <v>4.854</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>2.619</v>
+        <v>38.724</v>
       </c>
       <c r="H24" s="5" t="n"/>
       <c r="I24" s="5" t="n"/>
       <c r="J24" s="5" t="n"/>
       <c r="K24" s="5" t="inlineStr">
         <is>
-          <t>예상 도달 25.0분</t>
+          <t>2026-10-26 밸런스: 체력 계수 = 그 스테이지 시점 공격력(봇 실측)을 다듬은 값, 보상 배율 = 구간별 판당 수입 배율 목표(1~6 ×1.5, 7~11 ×1.35, 12~31 ×1.25, 32~46 ×1.15, 47~50 ×1.12)</t>
         </is>
       </c>
     </row>
@@ -1459,17 +1459,17 @@
         </is>
       </c>
       <c r="F25" s="5" t="n">
-        <v>2.67</v>
+        <v>4.854</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>2.67</v>
+        <v>46.311</v>
       </c>
       <c r="H25" s="5" t="n"/>
       <c r="I25" s="5" t="n"/>
       <c r="J25" s="5" t="n"/>
       <c r="K25" s="5" t="inlineStr">
         <is>
-          <t>예상 도달 25.5분</t>
+          <t>2026-10-26 밸런스: 체력 계수 = 그 스테이지 시점 공격력(봇 실측)을 다듬은 값, 보상 배율 = 구간별 판당 수입 배율 목표(1~6 ×1.5, 7~11 ×1.35, 12~31 ×1.25, 32~46 ×1.15, 47~50 ×1.12)</t>
         </is>
       </c>
     </row>
@@ -1496,17 +1496,17 @@
         </is>
       </c>
       <c r="F26" s="5" t="n">
-        <v>2.722</v>
+        <v>4.854</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>2.722</v>
+        <v>55.384</v>
       </c>
       <c r="H26" s="5" t="n"/>
       <c r="I26" s="5" t="n"/>
       <c r="J26" s="5" t="n"/>
       <c r="K26" s="5" t="inlineStr">
         <is>
-          <t>예상 도달 26.0분</t>
+          <t>2026-10-26 밸런스: 체력 계수 = 그 스테이지 시점 공격력(봇 실측)을 다듬은 값, 보상 배율 = 구간별 판당 수입 배율 목표(1~6 ×1.5, 7~11 ×1.35, 12~31 ×1.25, 32~46 ×1.15, 47~50 ×1.12)</t>
         </is>
       </c>
     </row>
@@ -1533,17 +1533,17 @@
         </is>
       </c>
       <c r="F27" s="5" t="n">
-        <v>2.774</v>
+        <v>5.212</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>2.774</v>
+        <v>71.11799999999999</v>
       </c>
       <c r="H27" s="5" t="n"/>
       <c r="I27" s="5" t="n"/>
       <c r="J27" s="5" t="n"/>
       <c r="K27" s="5" t="inlineStr">
         <is>
-          <t>예상 도달 26.5분</t>
+          <t>2026-10-26 밸런스: 체력 계수 = 그 스테이지 시점 공격력(봇 실측)을 다듬은 값, 보상 배율 = 구간별 판당 수입 배율 목표(1~6 ×1.5, 7~11 ×1.35, 12~31 ×1.25, 32~46 ×1.15, 47~50 ×1.12)</t>
         </is>
       </c>
     </row>
@@ -1570,17 +1570,17 @@
         </is>
       </c>
       <c r="F28" s="5" t="n">
-        <v>2.828</v>
+        <v>5.598</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>2.828</v>
+        <v>91.34999999999999</v>
       </c>
       <c r="H28" s="5" t="n"/>
       <c r="I28" s="5" t="n"/>
       <c r="J28" s="5" t="n"/>
       <c r="K28" s="5" t="inlineStr">
         <is>
-          <t>예상 도달 27.0분</t>
+          <t>2026-10-26 밸런스: 체력 계수 = 그 스테이지 시점 공격력(봇 실측)을 다듬은 값, 보상 배율 = 구간별 판당 수입 배율 목표(1~6 ×1.5, 7~11 ×1.35, 12~31 ×1.25, 32~46 ×1.15, 47~50 ×1.12)</t>
         </is>
       </c>
     </row>
@@ -1607,17 +1607,17 @@
         </is>
       </c>
       <c r="F29" s="5" t="n">
-        <v>2.883</v>
+        <v>6.012</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>2.883</v>
+        <v>117.326</v>
       </c>
       <c r="H29" s="5" t="n"/>
       <c r="I29" s="5" t="n"/>
       <c r="J29" s="5" t="n"/>
       <c r="K29" s="5" t="inlineStr">
         <is>
-          <t>예상 도달 27.5분</t>
+          <t>2026-10-26 밸런스: 체력 계수 = 그 스테이지 시점 공격력(봇 실측)을 다듬은 값, 보상 배율 = 구간별 판당 수입 배율 목표(1~6 ×1.5, 7~11 ×1.35, 12~31 ×1.25, 32~46 ×1.15, 47~50 ×1.12)</t>
         </is>
       </c>
     </row>
@@ -1644,17 +1644,17 @@
         </is>
       </c>
       <c r="F30" s="5" t="n">
-        <v>2.939</v>
+        <v>6.456</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>2.939</v>
+        <v>150.673</v>
       </c>
       <c r="H30" s="5" t="n"/>
       <c r="I30" s="5" t="n"/>
       <c r="J30" s="5" t="n"/>
       <c r="K30" s="5" t="inlineStr">
         <is>
-          <t>예상 도달 28.0분</t>
+          <t>2026-10-26 밸런스: 체력 계수 = 그 스테이지 시점 공격력(봇 실측)을 다듬은 값, 보상 배율 = 구간별 판당 수입 배율 목표(1~6 ×1.5, 7~11 ×1.35, 12~31 ×1.25, 32~46 ×1.15, 47~50 ×1.12)</t>
         </is>
       </c>
     </row>
@@ -1681,17 +1681,17 @@
         </is>
       </c>
       <c r="F31" s="5" t="n">
-        <v>2.997</v>
+        <v>6.934</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>2.997</v>
+        <v>193.53</v>
       </c>
       <c r="H31" s="5" t="n"/>
       <c r="I31" s="5" t="n"/>
       <c r="J31" s="5" t="n"/>
       <c r="K31" s="5" t="inlineStr">
         <is>
-          <t>예상 도달 28.5분</t>
+          <t>2026-10-26 밸런스: 체력 계수 = 그 스테이지 시점 공격력(봇 실측)을 다듬은 값, 보상 배율 = 구간별 판당 수입 배율 목표(1~6 ×1.5, 7~11 ×1.35, 12~31 ×1.25, 32~46 ×1.15, 47~50 ×1.12)</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
         </is>
       </c>
       <c r="F32" s="5" t="n">
-        <v>3.055</v>
+        <v>6.934</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>3.055</v>
+        <v>231.444</v>
       </c>
       <c r="H32" s="5" t="n"/>
       <c r="I32" s="5" t="n"/>
       <c r="J32" s="5" t="n"/>
       <c r="K32" s="5" t="inlineStr">
         <is>
-          <t>예상 도달 29.0분</t>
+          <t>2026-10-26 밸런스: 체력 계수 = 그 스테이지 시점 공격력(봇 실측)을 다듬은 값, 보상 배율 = 구간별 판당 수입 배율 목표(1~6 ×1.5, 7~11 ×1.35, 12~31 ×1.25, 32~46 ×1.15, 47~50 ×1.12)</t>
         </is>
       </c>
     </row>
@@ -1755,10 +1755,10 @@
         </is>
       </c>
       <c r="F33" s="6" t="n">
-        <v>3.114</v>
+        <v>6.934</v>
       </c>
       <c r="G33" s="6" t="n">
-        <v>3.114</v>
+        <v>276.782</v>
       </c>
       <c r="H33" s="6" t="n">
         <v>6003</v>
@@ -1767,7 +1767,7 @@
       <c r="J33" s="6" t="n"/>
       <c r="K33" s="6" t="inlineStr">
         <is>
-          <t>예상 도달 29.5분 · 보스 처치 목표 45분</t>
+          <t>2026-10-26 밸런스: 체력 계수 = 그 스테이지 시점 공격력(봇 실측)을 다듬은 값, 보상 배율 = 구간별 판당 수입 배율 목표(1~6 ×1.5, 7~11 ×1.35, 12~31 ×1.25, 32~46 ×1.15, 47~50 ×1.12)</t>
         </is>
       </c>
     </row>
@@ -1794,17 +1794,17 @@
         </is>
       </c>
       <c r="F34" s="5" t="n">
-        <v>5.657</v>
+        <v>6.934</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>5.657</v>
+        <v>331.006</v>
       </c>
       <c r="H34" s="5" t="n"/>
       <c r="I34" s="5" t="n"/>
       <c r="J34" s="5" t="n"/>
       <c r="K34" s="5" t="inlineStr">
         <is>
-          <t>예상 도달 45.0분</t>
+          <t>2026-10-26 밸런스: 체력 계수 = 그 스테이지 시점 공격력(봇 실측)을 다듬은 값, 보상 배율 = 구간별 판당 수입 배율 목표(1~6 ×1.5, 7~11 ×1.35, 12~31 ×1.25, 32~46 ×1.15, 47~50 ×1.12)</t>
         </is>
       </c>
     </row>
@@ -1831,17 +1831,17 @@
         </is>
       </c>
       <c r="F35" s="5" t="n">
-        <v>5.767</v>
+        <v>6.934</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>5.767</v>
+        <v>335.702</v>
       </c>
       <c r="H35" s="5" t="n"/>
       <c r="I35" s="5" t="n"/>
       <c r="J35" s="5" t="n"/>
       <c r="K35" s="5" t="inlineStr">
         <is>
-          <t>예상 도달 45.5분</t>
+          <t>2026-10-26 밸런스: 체력 계수 = 그 스테이지 시점 공격력(봇 실측)을 다듬은 값, 보상 배율 = 구간별 판당 수입 배율 목표(1~6 ×1.5, 7~11 ×1.35, 12~31 ×1.25, 32~46 ×1.15, 47~50 ×1.12)</t>
         </is>
       </c>
     </row>
@@ -1868,17 +1868,17 @@
         </is>
       </c>
       <c r="F36" s="5" t="n">
-        <v>5.879</v>
+        <v>6.934</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>5.879</v>
+        <v>340.462</v>
       </c>
       <c r="H36" s="5" t="n"/>
       <c r="I36" s="5" t="n"/>
       <c r="J36" s="5" t="n"/>
       <c r="K36" s="5" t="inlineStr">
         <is>
-          <t>예상 도달 46.0분</t>
+          <t>2026-10-26 밸런스: 체력 계수 = 그 스테이지 시점 공격력(봇 실측)을 다듬은 값, 보상 배율 = 구간별 판당 수입 배율 목표(1~6 ×1.5, 7~11 ×1.35, 12~31 ×1.25, 32~46 ×1.15, 47~50 ×1.12)</t>
         </is>
       </c>
     </row>
@@ -1905,17 +1905,17 @@
         </is>
       </c>
       <c r="F37" s="5" t="n">
-        <v>5.993</v>
+        <v>6.934</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>5.993</v>
+        <v>345.289</v>
       </c>
       <c r="H37" s="5" t="n"/>
       <c r="I37" s="5" t="n"/>
       <c r="J37" s="5" t="n"/>
       <c r="K37" s="5" t="inlineStr">
         <is>
-          <t>예상 도달 46.5분</t>
+          <t>2026-10-26 밸런스: 체력 계수 = 그 스테이지 시점 공격력(봇 실측)을 다듬은 값, 보상 배율 = 구간별 판당 수입 배율 목표(1~6 ×1.5, 7~11 ×1.35, 12~31 ×1.25, 32~46 ×1.15, 47~50 ×1.12)</t>
         </is>
       </c>
     </row>
@@ -1942,17 +1942,17 @@
         </is>
       </c>
       <c r="F38" s="5" t="n">
-        <v>6.11</v>
+        <v>6.934</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>6.11</v>
+        <v>350.184</v>
       </c>
       <c r="H38" s="5" t="n"/>
       <c r="I38" s="5" t="n"/>
       <c r="J38" s="5" t="n"/>
       <c r="K38" s="5" t="inlineStr">
         <is>
-          <t>예상 도달 47.0분</t>
+          <t>2026-10-26 밸런스: 체력 계수 = 그 스테이지 시점 공격력(봇 실측)을 다듬은 값, 보상 배율 = 구간별 판당 수입 배율 목표(1~6 ×1.5, 7~11 ×1.35, 12~31 ×1.25, 32~46 ×1.15, 47~50 ×1.12)</t>
         </is>
       </c>
     </row>
@@ -1979,17 +1979,17 @@
         </is>
       </c>
       <c r="F39" s="5" t="n">
-        <v>6.229</v>
+        <v>6.934</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>6.229</v>
+        <v>355.152</v>
       </c>
       <c r="H39" s="5" t="n"/>
       <c r="I39" s="5" t="n"/>
       <c r="J39" s="5" t="n"/>
       <c r="K39" s="5" t="inlineStr">
         <is>
-          <t>예상 도달 47.5분</t>
+          <t>2026-10-26 밸런스: 체력 계수 = 그 스테이지 시점 공격력(봇 실측)을 다듬은 값, 보상 배율 = 구간별 판당 수입 배율 목표(1~6 ×1.5, 7~11 ×1.35, 12~31 ×1.25, 32~46 ×1.15, 47~50 ×1.12)</t>
         </is>
       </c>
     </row>
@@ -2016,17 +2016,17 @@
         </is>
       </c>
       <c r="F40" s="5" t="n">
-        <v>6.35</v>
+        <v>6.934</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>6.35</v>
+        <v>360.186</v>
       </c>
       <c r="H40" s="5" t="n"/>
       <c r="I40" s="5" t="n"/>
       <c r="J40" s="5" t="n"/>
       <c r="K40" s="5" t="inlineStr">
         <is>
-          <t>예상 도달 48.0분</t>
+          <t>2026-10-26 밸런스: 체력 계수 = 그 스테이지 시점 공격력(봇 실측)을 다듬은 값, 보상 배율 = 구간별 판당 수입 배율 목표(1~6 ×1.5, 7~11 ×1.35, 12~31 ×1.25, 32~46 ×1.15, 47~50 ×1.12)</t>
         </is>
       </c>
     </row>
@@ -2053,17 +2053,17 @@
         </is>
       </c>
       <c r="F41" s="5" t="n">
-        <v>6.473</v>
+        <v>6.934</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>6.473</v>
+        <v>365.294</v>
       </c>
       <c r="H41" s="5" t="n"/>
       <c r="I41" s="5" t="n"/>
       <c r="J41" s="5" t="n"/>
       <c r="K41" s="5" t="inlineStr">
         <is>
-          <t>예상 도달 48.5분</t>
+          <t>2026-10-26 밸런스: 체력 계수 = 그 스테이지 시점 공격력(봇 실측)을 다듬은 값, 보상 배율 = 구간별 판당 수입 배율 목표(1~6 ×1.5, 7~11 ×1.35, 12~31 ×1.25, 32~46 ×1.15, 47~50 ×1.12)</t>
         </is>
       </c>
     </row>
@@ -2090,17 +2090,17 @@
         </is>
       </c>
       <c r="F42" s="5" t="n">
-        <v>6.599</v>
+        <v>6.934</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>6.599</v>
+        <v>370.473</v>
       </c>
       <c r="H42" s="5" t="n"/>
       <c r="I42" s="5" t="n"/>
       <c r="J42" s="5" t="n"/>
       <c r="K42" s="5" t="inlineStr">
         <is>
-          <t>예상 도달 49.0분</t>
+          <t>2026-10-26 밸런스: 체력 계수 = 그 스테이지 시점 공격력(봇 실측)을 다듬은 값, 보상 배율 = 구간별 판당 수입 배율 목표(1~6 ×1.5, 7~11 ×1.35, 12~31 ×1.25, 32~46 ×1.15, 47~50 ×1.12)</t>
         </is>
       </c>
     </row>
@@ -2127,10 +2127,10 @@
         </is>
       </c>
       <c r="F43" s="6" t="n">
-        <v>6.727</v>
+        <v>6.934</v>
       </c>
       <c r="G43" s="6" t="n">
-        <v>6.727</v>
+        <v>375.728</v>
       </c>
       <c r="H43" s="6" t="n">
         <v>6004</v>
@@ -2139,7 +2139,7 @@
       <c r="J43" s="6" t="n"/>
       <c r="K43" s="6" t="inlineStr">
         <is>
-          <t>예상 도달 49.5분 · 보스 처치 목표 67분</t>
+          <t>2026-10-26 밸런스: 체력 계수 = 그 스테이지 시점 공격력(봇 실측)을 다듬은 값, 보상 배율 = 구간별 판당 수입 배율 목표(1~6 ×1.5, 7~11 ×1.35, 12~31 ×1.25, 32~46 ×1.15, 47~50 ×1.12)</t>
         </is>
       </c>
     </row>
@@ -2166,17 +2166,17 @@
         </is>
       </c>
       <c r="F44" s="5" t="n">
-        <v>13.198</v>
+        <v>7.519</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>13.198</v>
+        <v>413.204</v>
       </c>
       <c r="H44" s="5" t="n"/>
       <c r="I44" s="5" t="n"/>
       <c r="J44" s="5" t="n"/>
       <c r="K44" s="5" t="inlineStr">
         <is>
-          <t>예상 도달 67.0분</t>
+          <t>2026-10-26 밸런스: 체력 계수 = 그 스테이지 시점 공격력(봇 실측)을 다듬은 값, 보상 배율 = 구간별 판당 수입 배율 목표(1~6 ×1.5, 7~11 ×1.35, 12~31 ×1.25, 32~46 ×1.15, 47~50 ×1.12)</t>
         </is>
       </c>
     </row>
@@ -2203,17 +2203,17 @@
         </is>
       </c>
       <c r="F45" s="5" t="n">
-        <v>13.454</v>
+        <v>8.154</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>13.454</v>
+        <v>454.455</v>
       </c>
       <c r="H45" s="5" t="n"/>
       <c r="I45" s="5" t="n"/>
       <c r="J45" s="5" t="n"/>
       <c r="K45" s="5" t="inlineStr">
         <is>
-          <t>예상 도달 67.5분</t>
+          <t>2026-10-26 밸런스: 체력 계수 = 그 스테이지 시점 공격력(봇 실측)을 다듬은 값, 보상 배율 = 구간별 판당 수입 배율 목표(1~6 ×1.5, 7~11 ×1.35, 12~31 ×1.25, 32~46 ×1.15, 47~50 ×1.12)</t>
         </is>
       </c>
     </row>
@@ -2240,17 +2240,17 @@
         </is>
       </c>
       <c r="F46" s="5" t="n">
-        <v>13.716</v>
+        <v>8.843</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>13.716</v>
+        <v>499.844</v>
       </c>
       <c r="H46" s="5" t="n"/>
       <c r="I46" s="5" t="n"/>
       <c r="J46" s="5" t="n"/>
       <c r="K46" s="5" t="inlineStr">
         <is>
-          <t>예상 도달 68.0분</t>
+          <t>2026-10-26 밸런스: 체력 계수 = 그 스테이지 시점 공격력(봇 실측)을 다듬은 값, 보상 배율 = 구간별 판당 수입 배율 목표(1~6 ×1.5, 7~11 ×1.35, 12~31 ×1.25, 32~46 ×1.15, 47~50 ×1.12)</t>
         </is>
       </c>
     </row>
@@ -2277,17 +2277,17 @@
         </is>
       </c>
       <c r="F47" s="5" t="n">
-        <v>13.983</v>
+        <v>9.59</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>13.983</v>
+        <v>549.753</v>
       </c>
       <c r="H47" s="5" t="n"/>
       <c r="I47" s="5" t="n"/>
       <c r="J47" s="5" t="n"/>
       <c r="K47" s="5" t="inlineStr">
         <is>
-          <t>예상 도달 68.5분</t>
+          <t>2026-10-26 밸런스: 체력 계수 = 그 스테이지 시점 공격력(봇 실측)을 다듬은 값, 보상 배율 = 구간별 판당 수입 배율 목표(1~6 ×1.5, 7~11 ×1.35, 12~31 ×1.25, 32~46 ×1.15, 47~50 ×1.12)</t>
         </is>
       </c>
     </row>
@@ -2314,17 +2314,17 @@
         </is>
       </c>
       <c r="F48" s="5" t="n">
-        <v>14.254</v>
+        <v>10.4</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>14.254</v>
+        <v>604.644</v>
       </c>
       <c r="H48" s="5" t="n"/>
       <c r="I48" s="5" t="n"/>
       <c r="J48" s="5" t="n"/>
       <c r="K48" s="5" t="inlineStr">
         <is>
-          <t>예상 도달 69.0분</t>
+          <t>2026-10-26 밸런스: 체력 계수 = 그 스테이지 시점 공격력(봇 실측)을 다듬은 값, 보상 배율 = 구간별 판당 수입 배율 목표(1~6 ×1.5, 7~11 ×1.35, 12~31 ×1.25, 32~46 ×1.15, 47~50 ×1.12)</t>
         </is>
       </c>
     </row>
@@ -2351,17 +2351,17 @@
         </is>
       </c>
       <c r="F49" s="5" t="n">
-        <v>14.531</v>
+        <v>10.4</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>14.531</v>
+        <v>613.218</v>
       </c>
       <c r="H49" s="5" t="n"/>
       <c r="I49" s="5" t="n"/>
       <c r="J49" s="5" t="n"/>
       <c r="K49" s="5" t="inlineStr">
         <is>
-          <t>예상 도달 69.5분</t>
+          <t>2026-10-26 밸런스: 체력 계수 = 그 스테이지 시점 공격력(봇 실측)을 다듬은 값, 보상 배율 = 구간별 판당 수입 배율 목표(1~6 ×1.5, 7~11 ×1.35, 12~31 ×1.25, 32~46 ×1.15, 47~50 ×1.12)</t>
         </is>
       </c>
     </row>
@@ -2388,17 +2388,17 @@
         </is>
       </c>
       <c r="F50" s="5" t="n">
-        <v>14.814</v>
+        <v>10.4</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>14.814</v>
+        <v>641.8630000000001</v>
       </c>
       <c r="H50" s="5" t="n"/>
       <c r="I50" s="5" t="n"/>
       <c r="J50" s="5" t="n"/>
       <c r="K50" s="5" t="inlineStr">
         <is>
-          <t>예상 도달 70.0분</t>
+          <t>2026-10-26 밸런스: 체력 계수 = 그 스테이지 시점 공격력(봇 실측)을 다듬은 값, 보상 배율 = 구간별 판당 수입 배율 목표(1~6 ×1.5, 7~11 ×1.35, 12~31 ×1.25, 32~46 ×1.15, 47~50 ×1.12)</t>
         </is>
       </c>
     </row>
@@ -2425,17 +2425,17 @@
         </is>
       </c>
       <c r="F51" s="5" t="n">
-        <v>15.102</v>
+        <v>10.4</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>15.102</v>
+        <v>671.848</v>
       </c>
       <c r="H51" s="5" t="n"/>
       <c r="I51" s="5" t="n"/>
       <c r="J51" s="5" t="n"/>
       <c r="K51" s="5" t="inlineStr">
         <is>
-          <t>예상 도달 70.5분</t>
+          <t>2026-10-26 밸런스: 체력 계수 = 그 스테이지 시점 공격력(봇 실측)을 다듬은 값, 보상 배율 = 구간별 판당 수입 배율 목표(1~6 ×1.5, 7~11 ×1.35, 12~31 ×1.25, 32~46 ×1.15, 47~50 ×1.12)</t>
         </is>
       </c>
     </row>
@@ -2462,17 +2462,17 @@
         </is>
       </c>
       <c r="F52" s="5" t="n">
-        <v>15.396</v>
+        <v>10.4</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>15.396</v>
+        <v>703.234</v>
       </c>
       <c r="H52" s="5" t="n"/>
       <c r="I52" s="5" t="n"/>
       <c r="J52" s="5" t="n"/>
       <c r="K52" s="5" t="inlineStr">
         <is>
-          <t>예상 도달 71.0분</t>
+          <t>2026-10-26 밸런스: 체력 계수 = 그 스테이지 시점 공격력(봇 실측)을 다듬은 값, 보상 배율 = 구간별 판당 수입 배율 목표(1~6 ×1.5, 7~11 ×1.35, 12~31 ×1.25, 32~46 ×1.15, 47~50 ×1.12)</t>
         </is>
       </c>
     </row>
@@ -2499,10 +2499,10 @@
         </is>
       </c>
       <c r="F53" s="6" t="n">
-        <v>15.695</v>
+        <v>10.4</v>
       </c>
       <c r="G53" s="6" t="n">
-        <v>15.695</v>
+        <v>736.085</v>
       </c>
       <c r="H53" s="6" t="n">
         <v>6005</v>
@@ -2511,7 +2511,7 @@
       <c r="J53" s="6" t="n"/>
       <c r="K53" s="6" t="inlineStr">
         <is>
-          <t>예상 도달 71.5분 · 보스 처치 목표 90분</t>
+          <t>2026-10-26 밸런스: 체력 계수 = 그 스테이지 시점 공격력(봇 실측)을 다듬은 값, 보상 배율 = 구간별 판당 수입 배율 목표(1~6 ×1.5, 7~11 ×1.35, 12~31 ×1.25, 32~46 ×1.15, 47~50 ×1.12)</t>
         </is>
       </c>
     </row>

--- a/Assets/Data/Tables/Stage.xlsx
+++ b/Assets/Data/Tables/Stage.xlsx
@@ -472,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K53"/>
+  <dimension ref="A1:O53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -531,15 +531,35 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
+          <t>goalType</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>goal</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>mushHpMul</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>gem</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
           <t>icon</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>desc</t>
         </is>
       </c>
-      <c r="K1" s="2" t="inlineStr">
+      <c r="O1" s="2" t="inlineStr">
         <is>
           <t>#memo</t>
         </is>
@@ -588,15 +608,35 @@
       </c>
       <c r="I2" s="3" t="inlineStr">
         <is>
+          <t>StageGoal</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
           <t>string</t>
         </is>
       </c>
-      <c r="J2" s="3" t="inlineStr">
+      <c r="N2" s="3" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="K2" s="3" t="n"/>
+      <c r="O2" s="3" t="n"/>
     </row>
     <row r="3" ht="48" customHeight="1">
       <c r="A3" s="4" t="inlineStr">
@@ -641,15 +681,35 @@
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
+          <t>클리어 조건 (None / Harvest = 버섯 n개). 보스 스테이지는 비움</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>목표 수치. 연속 실패마다 ×0.9 (최저 0.7, RoundBase)</t>
+        </is>
+      </c>
+      <c r="K3" s="4" t="inlineStr">
+        <is>
+          <t>일반 버섯 체력 배율 (보스 제외). 비우면 1</t>
+        </is>
+      </c>
+      <c r="L3" s="4" t="inlineStr">
+        <is>
+          <t>첫 클리어 균사석 (★ 스테이지). 보스는 Boss.xlsx gem</t>
+        </is>
+      </c>
+      <c r="M3" s="4" t="inlineStr">
+        <is>
           <t>아이콘 경로 (Resources 기준)</t>
         </is>
       </c>
-      <c r="J3" s="4" t="inlineStr">
+      <c r="N3" s="4" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
       </c>
-      <c r="K3" s="4" t="inlineStr">
+      <c r="O3" s="4" t="inlineStr">
         <is>
           <t>기획 메모 (게임에서 읽지 않음)</t>
         </is>
@@ -684,9 +744,19 @@
         <v>1</v>
       </c>
       <c r="H4" s="5" t="n"/>
-      <c r="I4" s="5" t="n"/>
-      <c r="J4" s="5" t="n"/>
-      <c r="K4" s="5" t="inlineStr">
+      <c r="I4" s="5" t="inlineStr">
+        <is>
+          <t>Harvest</t>
+        </is>
+      </c>
+      <c r="J4" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="K4" s="5" t="n"/>
+      <c r="L4" s="5" t="n"/>
+      <c r="M4" s="5" t="n"/>
+      <c r="N4" s="5" t="n"/>
+      <c r="O4" s="5" t="inlineStr">
         <is>
           <t>2026-10-26 밸런스: 체력 계수 = 그 스테이지 시점 공격력(봇 실측)을 다듬은 값, 보상 배율 = 구간별 판당 수입 배율 목표(1~6 ×1.5, 7~11 ×1.35, 12~31 ×1.25, 32~46 ×1.15, 47~50 ×1.12)</t>
         </is>
@@ -721,9 +791,19 @@
         <v>1.286</v>
       </c>
       <c r="H5" s="5" t="n"/>
-      <c r="I5" s="5" t="n"/>
-      <c r="J5" s="5" t="n"/>
-      <c r="K5" s="5" t="inlineStr">
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>Harvest</t>
+        </is>
+      </c>
+      <c r="J5" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="K5" s="5" t="n"/>
+      <c r="L5" s="5" t="n"/>
+      <c r="M5" s="5" t="n"/>
+      <c r="N5" s="5" t="n"/>
+      <c r="O5" s="5" t="inlineStr">
         <is>
           <t>2026-10-26 밸런스: 체력 계수 = 그 스테이지 시점 공격력(봇 실측)을 다듬은 값, 보상 배율 = 구간별 판당 수입 배율 목표(1~6 ×1.5, 7~11 ×1.35, 12~31 ×1.25, 32~46 ×1.15, 47~50 ×1.12)</t>
         </is>
@@ -758,9 +838,19 @@
         <v>1.535</v>
       </c>
       <c r="H6" s="5" t="n"/>
-      <c r="I6" s="5" t="n"/>
-      <c r="J6" s="5" t="n"/>
-      <c r="K6" s="5" t="inlineStr">
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>Harvest</t>
+        </is>
+      </c>
+      <c r="J6" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="K6" s="5" t="n"/>
+      <c r="L6" s="5" t="n"/>
+      <c r="M6" s="5" t="n"/>
+      <c r="N6" s="5" t="n"/>
+      <c r="O6" s="5" t="inlineStr">
         <is>
           <t>2026-10-26 밸런스: 체력 계수 = 그 스테이지 시점 공격력(봇 실측)을 다듬은 값, 보상 배율 = 구간별 판당 수입 배율 목표(1~6 ×1.5, 7~11 ×1.35, 12~31 ×1.25, 32~46 ×1.15, 47~50 ×1.12)</t>
         </is>
@@ -795,9 +885,21 @@
         <v>2.048</v>
       </c>
       <c r="H7" s="5" t="n"/>
-      <c r="I7" s="5" t="n"/>
-      <c r="J7" s="5" t="n"/>
-      <c r="K7" s="5" t="inlineStr">
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>Harvest</t>
+        </is>
+      </c>
+      <c r="J7" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="L7" s="5" t="n"/>
+      <c r="M7" s="5" t="n"/>
+      <c r="N7" s="5" t="n"/>
+      <c r="O7" s="5" t="inlineStr">
         <is>
           <t>2026-10-26 밸런스: 체력 계수 = 그 스테이지 시점 공격력(봇 실측)을 다듬은 값, 보상 배율 = 구간별 판당 수입 배율 목표(1~6 ×1.5, 7~11 ×1.35, 12~31 ×1.25, 32~46 ×1.15, 47~50 ×1.12)</t>
         </is>
@@ -832,9 +934,23 @@
         <v>3.024</v>
       </c>
       <c r="H8" s="5" t="n"/>
-      <c r="I8" s="5" t="n"/>
-      <c r="J8" s="5" t="n"/>
-      <c r="K8" s="5" t="inlineStr">
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t>Harvest</t>
+        </is>
+      </c>
+      <c r="J8" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="K8" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="L8" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="M8" s="5" t="n"/>
+      <c r="N8" s="5" t="n"/>
+      <c r="O8" s="5" t="inlineStr">
         <is>
           <t>2026-10-26 밸런스: 체력 계수 = 그 스테이지 시점 공격력(봇 실측)을 다듬은 값, 보상 배율 = 구간별 판당 수입 배율 목표(1~6 ×1.5, 7~11 ×1.35, 12~31 ×1.25, 32~46 ×1.15, 47~50 ×1.12)</t>
         </is>
@@ -869,9 +985,19 @@
         <v>3.586</v>
       </c>
       <c r="H9" s="5" t="n"/>
-      <c r="I9" s="5" t="n"/>
-      <c r="J9" s="5" t="n"/>
-      <c r="K9" s="5" t="inlineStr">
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>Harvest</t>
+        </is>
+      </c>
+      <c r="J9" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="K9" s="5" t="n"/>
+      <c r="L9" s="5" t="n"/>
+      <c r="M9" s="5" t="n"/>
+      <c r="N9" s="5" t="n"/>
+      <c r="O9" s="5" t="inlineStr">
         <is>
           <t>2026-10-26 밸런스: 체력 계수 = 그 스테이지 시점 공격력(봇 실측)을 다듬은 값, 보상 배율 = 구간별 판당 수입 배율 목표(1~6 ×1.5, 7~11 ×1.35, 12~31 ×1.25, 32~46 ×1.15, 47~50 ×1.12)</t>
         </is>
@@ -906,9 +1032,19 @@
         <v>3.928</v>
       </c>
       <c r="H10" s="5" t="n"/>
-      <c r="I10" s="5" t="n"/>
-      <c r="J10" s="5" t="n"/>
-      <c r="K10" s="5" t="inlineStr">
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>Harvest</t>
+        </is>
+      </c>
+      <c r="J10" s="5" t="n">
+        <v>29</v>
+      </c>
+      <c r="K10" s="5" t="n"/>
+      <c r="L10" s="5" t="n"/>
+      <c r="M10" s="5" t="n"/>
+      <c r="N10" s="5" t="n"/>
+      <c r="O10" s="5" t="inlineStr">
         <is>
           <t>2026-10-26 밸런스: 체력 계수 = 그 스테이지 시점 공격력(봇 실측)을 다듬은 값, 보상 배율 = 구간별 판당 수입 배율 목표(1~6 ×1.5, 7~11 ×1.35, 12~31 ×1.25, 32~46 ×1.15, 47~50 ×1.12)</t>
         </is>
@@ -943,9 +1079,21 @@
         <v>4.306</v>
       </c>
       <c r="H11" s="5" t="n"/>
-      <c r="I11" s="5" t="n"/>
-      <c r="J11" s="5" t="n"/>
-      <c r="K11" s="5" t="inlineStr">
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>Harvest</t>
+        </is>
+      </c>
+      <c r="J11" s="5" t="n">
+        <v>34</v>
+      </c>
+      <c r="K11" s="5" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="L11" s="5" t="n"/>
+      <c r="M11" s="5" t="n"/>
+      <c r="N11" s="5" t="n"/>
+      <c r="O11" s="5" t="inlineStr">
         <is>
           <t>2026-10-26 밸런스: 체력 계수 = 그 스테이지 시점 공격력(봇 실측)을 다듬은 값, 보상 배율 = 구간별 판당 수입 배율 목표(1~6 ×1.5, 7~11 ×1.35, 12~31 ×1.25, 32~46 ×1.15, 47~50 ×1.12)</t>
         </is>
@@ -980,9 +1128,21 @@
         <v>5.048</v>
       </c>
       <c r="H12" s="5" t="n"/>
-      <c r="I12" s="5" t="n"/>
-      <c r="J12" s="5" t="n"/>
-      <c r="K12" s="5" t="inlineStr">
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t>Harvest</t>
+        </is>
+      </c>
+      <c r="J12" s="5" t="n">
+        <v>32</v>
+      </c>
+      <c r="K12" s="5" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="L12" s="5" t="n"/>
+      <c r="M12" s="5" t="n"/>
+      <c r="N12" s="5" t="n"/>
+      <c r="O12" s="5" t="inlineStr">
         <is>
           <t>2026-10-26 밸런스: 체력 계수 = 그 스테이지 시점 공격력(봇 실측)을 다듬은 값, 보상 배율 = 구간별 판당 수입 배율 목표(1~6 ×1.5, 7~11 ×1.35, 12~31 ×1.25, 32~46 ×1.15, 47~50 ×1.12)</t>
         </is>
@@ -1021,7 +1181,11 @@
       </c>
       <c r="I13" s="6" t="n"/>
       <c r="J13" s="6" t="n"/>
-      <c r="K13" s="6" t="inlineStr">
+      <c r="K13" s="6" t="n"/>
+      <c r="L13" s="6" t="n"/>
+      <c r="M13" s="6" t="n"/>
+      <c r="N13" s="6" t="n"/>
+      <c r="O13" s="6" t="inlineStr">
         <is>
           <t>2026-10-26 밸런스: 체력 계수 = 그 스테이지 시점 공격력(봇 실측)을 다듬은 값, 보상 배율 = 구간별 판당 수입 배율 목표(1~6 ×1.5, 7~11 ×1.35, 12~31 ×1.25, 32~46 ×1.15, 47~50 ×1.12)</t>
         </is>
@@ -1056,9 +1220,19 @@
         <v>5.655</v>
       </c>
       <c r="H14" s="5" t="n"/>
-      <c r="I14" s="5" t="n"/>
-      <c r="J14" s="5" t="n"/>
-      <c r="K14" s="5" t="inlineStr">
+      <c r="I14" s="5" t="inlineStr">
+        <is>
+          <t>Harvest</t>
+        </is>
+      </c>
+      <c r="J14" s="5" t="n">
+        <v>37</v>
+      </c>
+      <c r="K14" s="5" t="n"/>
+      <c r="L14" s="5" t="n"/>
+      <c r="M14" s="5" t="n"/>
+      <c r="N14" s="5" t="n"/>
+      <c r="O14" s="5" t="inlineStr">
         <is>
           <t>2026-10-26 밸런스: 체력 계수 = 그 스테이지 시점 공격력(봇 실측)을 다듬은 값, 보상 배율 = 구간별 판당 수입 배율 목표(1~6 ×1.5, 7~11 ×1.35, 12~31 ×1.25, 32~46 ×1.15, 47~50 ×1.12)</t>
         </is>
@@ -1093,9 +1267,19 @@
         <v>7.236</v>
       </c>
       <c r="H15" s="5" t="n"/>
-      <c r="I15" s="5" t="n"/>
-      <c r="J15" s="5" t="n"/>
-      <c r="K15" s="5" t="inlineStr">
+      <c r="I15" s="5" t="inlineStr">
+        <is>
+          <t>Harvest</t>
+        </is>
+      </c>
+      <c r="J15" s="5" t="n">
+        <v>37</v>
+      </c>
+      <c r="K15" s="5" t="n"/>
+      <c r="L15" s="5" t="n"/>
+      <c r="M15" s="5" t="n"/>
+      <c r="N15" s="5" t="n"/>
+      <c r="O15" s="5" t="inlineStr">
         <is>
           <t>2026-10-26 밸런스: 체력 계수 = 그 스테이지 시점 공격력(봇 실측)을 다듬은 값, 보상 배율 = 구간별 판당 수입 배율 목표(1~6 ×1.5, 7~11 ×1.35, 12~31 ×1.25, 32~46 ×1.15, 47~50 ×1.12)</t>
         </is>
@@ -1130,9 +1314,19 @@
         <v>9.256</v>
       </c>
       <c r="H16" s="5" t="n"/>
-      <c r="I16" s="5" t="n"/>
-      <c r="J16" s="5" t="n"/>
-      <c r="K16" s="5" t="inlineStr">
+      <c r="I16" s="5" t="inlineStr">
+        <is>
+          <t>Harvest</t>
+        </is>
+      </c>
+      <c r="J16" s="5" t="n">
+        <v>37</v>
+      </c>
+      <c r="K16" s="5" t="n"/>
+      <c r="L16" s="5" t="n"/>
+      <c r="M16" s="5" t="n"/>
+      <c r="N16" s="5" t="n"/>
+      <c r="O16" s="5" t="inlineStr">
         <is>
           <t>2026-10-26 밸런스: 체력 계수 = 그 스테이지 시점 공격력(봇 실측)을 다듬은 값, 보상 배율 = 구간별 판당 수입 배율 목표(1~6 ×1.5, 7~11 ×1.35, 12~31 ×1.25, 32~46 ×1.15, 47~50 ×1.12)</t>
         </is>
@@ -1167,9 +1361,21 @@
         <v>11.07</v>
       </c>
       <c r="H17" s="5" t="n"/>
-      <c r="I17" s="5" t="n"/>
-      <c r="J17" s="5" t="n"/>
-      <c r="K17" s="5" t="inlineStr">
+      <c r="I17" s="5" t="inlineStr">
+        <is>
+          <t>Harvest</t>
+        </is>
+      </c>
+      <c r="J17" s="5" t="n">
+        <v>39</v>
+      </c>
+      <c r="K17" s="5" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="L17" s="5" t="n"/>
+      <c r="M17" s="5" t="n"/>
+      <c r="N17" s="5" t="n"/>
+      <c r="O17" s="5" t="inlineStr">
         <is>
           <t>2026-10-26 밸런스: 체력 계수 = 그 스테이지 시점 공격력(봇 실측)을 다듬은 값, 보상 배율 = 구간별 판당 수입 배율 목표(1~6 ×1.5, 7~11 ×1.35, 12~31 ×1.25, 32~46 ×1.15, 47~50 ×1.12)</t>
         </is>
@@ -1204,9 +1410,23 @@
         <v>13.238</v>
       </c>
       <c r="H18" s="5" t="n"/>
-      <c r="I18" s="5" t="n"/>
-      <c r="J18" s="5" t="n"/>
-      <c r="K18" s="5" t="inlineStr">
+      <c r="I18" s="5" t="inlineStr">
+        <is>
+          <t>Harvest</t>
+        </is>
+      </c>
+      <c r="J18" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="K18" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="L18" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="M18" s="5" t="n"/>
+      <c r="N18" s="5" t="n"/>
+      <c r="O18" s="5" t="inlineStr">
         <is>
           <t>2026-10-26 밸런스: 체력 계수 = 그 스테이지 시점 공격력(봇 실측)을 다듬은 값, 보상 배율 = 구간별 판당 수입 배율 목표(1~6 ×1.5, 7~11 ×1.35, 12~31 ×1.25, 32~46 ×1.15, 47~50 ×1.12)</t>
         </is>
@@ -1241,9 +1461,19 @@
         <v>15.832</v>
       </c>
       <c r="H19" s="5" t="n"/>
-      <c r="I19" s="5" t="n"/>
-      <c r="J19" s="5" t="n"/>
-      <c r="K19" s="5" t="inlineStr">
+      <c r="I19" s="5" t="inlineStr">
+        <is>
+          <t>Harvest</t>
+        </is>
+      </c>
+      <c r="J19" s="5" t="n">
+        <v>45</v>
+      </c>
+      <c r="K19" s="5" t="n"/>
+      <c r="L19" s="5" t="n"/>
+      <c r="M19" s="5" t="n"/>
+      <c r="N19" s="5" t="n"/>
+      <c r="O19" s="5" t="inlineStr">
         <is>
           <t>2026-10-26 밸런스: 체력 계수 = 그 스테이지 시점 공격력(봇 실측)을 다듬은 값, 보상 배율 = 구간별 판당 수입 배율 목표(1~6 ×1.5, 7~11 ×1.35, 12~31 ×1.25, 32~46 ×1.15, 47~50 ×1.12)</t>
         </is>
@@ -1278,9 +1508,19 @@
         <v>18.932</v>
       </c>
       <c r="H20" s="5" t="n"/>
-      <c r="I20" s="5" t="n"/>
-      <c r="J20" s="5" t="n"/>
-      <c r="K20" s="5" t="inlineStr">
+      <c r="I20" s="5" t="inlineStr">
+        <is>
+          <t>Harvest</t>
+        </is>
+      </c>
+      <c r="J20" s="5" t="n">
+        <v>54</v>
+      </c>
+      <c r="K20" s="5" t="n"/>
+      <c r="L20" s="5" t="n"/>
+      <c r="M20" s="5" t="n"/>
+      <c r="N20" s="5" t="n"/>
+      <c r="O20" s="5" t="inlineStr">
         <is>
           <t>2026-10-26 밸런스: 체력 계수 = 그 스테이지 시점 공격력(봇 실측)을 다듬은 값, 보상 배율 = 구간별 판당 수입 배율 목표(1~6 ×1.5, 7~11 ×1.35, 12~31 ×1.25, 32~46 ×1.15, 47~50 ×1.12)</t>
         </is>
@@ -1315,9 +1555,21 @@
         <v>22.642</v>
       </c>
       <c r="H21" s="5" t="n"/>
-      <c r="I21" s="5" t="n"/>
-      <c r="J21" s="5" t="n"/>
-      <c r="K21" s="5" t="inlineStr">
+      <c r="I21" s="5" t="inlineStr">
+        <is>
+          <t>Harvest</t>
+        </is>
+      </c>
+      <c r="J21" s="5" t="n">
+        <v>64</v>
+      </c>
+      <c r="K21" s="5" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="L21" s="5" t="n"/>
+      <c r="M21" s="5" t="n"/>
+      <c r="N21" s="5" t="n"/>
+      <c r="O21" s="5" t="inlineStr">
         <is>
           <t>2026-10-26 밸런스: 체력 계수 = 그 스테이지 시점 공격력(봇 실측)을 다듬은 값, 보상 배율 = 구간별 판당 수입 배율 목표(1~6 ×1.5, 7~11 ×1.35, 12~31 ×1.25, 32~46 ×1.15, 47~50 ×1.12)</t>
         </is>
@@ -1352,9 +1604,21 @@
         <v>27.076</v>
       </c>
       <c r="H22" s="5" t="n"/>
-      <c r="I22" s="5" t="n"/>
-      <c r="J22" s="5" t="n"/>
-      <c r="K22" s="5" t="inlineStr">
+      <c r="I22" s="5" t="inlineStr">
+        <is>
+          <t>Harvest</t>
+        </is>
+      </c>
+      <c r="J22" s="5" t="n">
+        <v>65</v>
+      </c>
+      <c r="K22" s="5" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="L22" s="5" t="n"/>
+      <c r="M22" s="5" t="n"/>
+      <c r="N22" s="5" t="n"/>
+      <c r="O22" s="5" t="inlineStr">
         <is>
           <t>2026-10-26 밸런스: 체력 계수 = 그 스테이지 시점 공격력(봇 실측)을 다듬은 값, 보상 배율 = 구간별 판당 수입 배율 목표(1~6 ×1.5, 7~11 ×1.35, 12~31 ×1.25, 32~46 ×1.15, 47~50 ×1.12)</t>
         </is>
@@ -1393,7 +1657,11 @@
       </c>
       <c r="I23" s="6" t="n"/>
       <c r="J23" s="6" t="n"/>
-      <c r="K23" s="6" t="inlineStr">
+      <c r="K23" s="6" t="n"/>
+      <c r="L23" s="6" t="n"/>
+      <c r="M23" s="6" t="n"/>
+      <c r="N23" s="6" t="n"/>
+      <c r="O23" s="6" t="inlineStr">
         <is>
           <t>2026-10-26 밸런스: 체력 계수 = 그 스테이지 시점 공격력(봇 실측)을 다듬은 값, 보상 배율 = 구간별 판당 수입 배율 목표(1~6 ×1.5, 7~11 ×1.35, 12~31 ×1.25, 32~46 ×1.15, 47~50 ×1.12)</t>
         </is>
@@ -1428,9 +1696,19 @@
         <v>38.724</v>
       </c>
       <c r="H24" s="5" t="n"/>
-      <c r="I24" s="5" t="n"/>
-      <c r="J24" s="5" t="n"/>
-      <c r="K24" s="5" t="inlineStr">
+      <c r="I24" s="5" t="inlineStr">
+        <is>
+          <t>Harvest</t>
+        </is>
+      </c>
+      <c r="J24" s="5" t="n">
+        <v>83</v>
+      </c>
+      <c r="K24" s="5" t="n"/>
+      <c r="L24" s="5" t="n"/>
+      <c r="M24" s="5" t="n"/>
+      <c r="N24" s="5" t="n"/>
+      <c r="O24" s="5" t="inlineStr">
         <is>
           <t>2026-10-26 밸런스: 체력 계수 = 그 스테이지 시점 공격력(봇 실측)을 다듬은 값, 보상 배율 = 구간별 판당 수입 배율 목표(1~6 ×1.5, 7~11 ×1.35, 12~31 ×1.25, 32~46 ×1.15, 47~50 ×1.12)</t>
         </is>
@@ -1465,9 +1743,19 @@
         <v>46.311</v>
       </c>
       <c r="H25" s="5" t="n"/>
-      <c r="I25" s="5" t="n"/>
-      <c r="J25" s="5" t="n"/>
-      <c r="K25" s="5" t="inlineStr">
+      <c r="I25" s="5" t="inlineStr">
+        <is>
+          <t>Harvest</t>
+        </is>
+      </c>
+      <c r="J25" s="5" t="n">
+        <v>89</v>
+      </c>
+      <c r="K25" s="5" t="n"/>
+      <c r="L25" s="5" t="n"/>
+      <c r="M25" s="5" t="n"/>
+      <c r="N25" s="5" t="n"/>
+      <c r="O25" s="5" t="inlineStr">
         <is>
           <t>2026-10-26 밸런스: 체력 계수 = 그 스테이지 시점 공격력(봇 실측)을 다듬은 값, 보상 배율 = 구간별 판당 수입 배율 목표(1~6 ×1.5, 7~11 ×1.35, 12~31 ×1.25, 32~46 ×1.15, 47~50 ×1.12)</t>
         </is>
@@ -1502,9 +1790,19 @@
         <v>55.384</v>
       </c>
       <c r="H26" s="5" t="n"/>
-      <c r="I26" s="5" t="n"/>
-      <c r="J26" s="5" t="n"/>
-      <c r="K26" s="5" t="inlineStr">
+      <c r="I26" s="5" t="inlineStr">
+        <is>
+          <t>Harvest</t>
+        </is>
+      </c>
+      <c r="J26" s="5" t="n">
+        <v>95</v>
+      </c>
+      <c r="K26" s="5" t="n"/>
+      <c r="L26" s="5" t="n"/>
+      <c r="M26" s="5" t="n"/>
+      <c r="N26" s="5" t="n"/>
+      <c r="O26" s="5" t="inlineStr">
         <is>
           <t>2026-10-26 밸런스: 체력 계수 = 그 스테이지 시점 공격력(봇 실측)을 다듬은 값, 보상 배율 = 구간별 판당 수입 배율 목표(1~6 ×1.5, 7~11 ×1.35, 12~31 ×1.25, 32~46 ×1.15, 47~50 ×1.12)</t>
         </is>
@@ -1539,9 +1837,21 @@
         <v>71.11799999999999</v>
       </c>
       <c r="H27" s="5" t="n"/>
-      <c r="I27" s="5" t="n"/>
-      <c r="J27" s="5" t="n"/>
-      <c r="K27" s="5" t="inlineStr">
+      <c r="I27" s="5" t="inlineStr">
+        <is>
+          <t>Harvest</t>
+        </is>
+      </c>
+      <c r="J27" s="5" t="n">
+        <v>103</v>
+      </c>
+      <c r="K27" s="5" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="L27" s="5" t="n"/>
+      <c r="M27" s="5" t="n"/>
+      <c r="N27" s="5" t="n"/>
+      <c r="O27" s="5" t="inlineStr">
         <is>
           <t>2026-10-26 밸런스: 체력 계수 = 그 스테이지 시점 공격력(봇 실측)을 다듬은 값, 보상 배율 = 구간별 판당 수입 배율 목표(1~6 ×1.5, 7~11 ×1.35, 12~31 ×1.25, 32~46 ×1.15, 47~50 ×1.12)</t>
         </is>
@@ -1576,9 +1886,23 @@
         <v>91.34999999999999</v>
       </c>
       <c r="H28" s="5" t="n"/>
-      <c r="I28" s="5" t="n"/>
-      <c r="J28" s="5" t="n"/>
-      <c r="K28" s="5" t="inlineStr">
+      <c r="I28" s="5" t="inlineStr">
+        <is>
+          <t>Harvest</t>
+        </is>
+      </c>
+      <c r="J28" s="5" t="n">
+        <v>130</v>
+      </c>
+      <c r="K28" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="L28" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="M28" s="5" t="n"/>
+      <c r="N28" s="5" t="n"/>
+      <c r="O28" s="5" t="inlineStr">
         <is>
           <t>2026-10-26 밸런스: 체력 계수 = 그 스테이지 시점 공격력(봇 실측)을 다듬은 값, 보상 배율 = 구간별 판당 수입 배율 목표(1~6 ×1.5, 7~11 ×1.35, 12~31 ×1.25, 32~46 ×1.15, 47~50 ×1.12)</t>
         </is>
@@ -1613,9 +1937,19 @@
         <v>117.326</v>
       </c>
       <c r="H29" s="5" t="n"/>
-      <c r="I29" s="5" t="n"/>
-      <c r="J29" s="5" t="n"/>
-      <c r="K29" s="5" t="inlineStr">
+      <c r="I29" s="5" t="inlineStr">
+        <is>
+          <t>Harvest</t>
+        </is>
+      </c>
+      <c r="J29" s="5" t="n">
+        <v>127</v>
+      </c>
+      <c r="K29" s="5" t="n"/>
+      <c r="L29" s="5" t="n"/>
+      <c r="M29" s="5" t="n"/>
+      <c r="N29" s="5" t="n"/>
+      <c r="O29" s="5" t="inlineStr">
         <is>
           <t>2026-10-26 밸런스: 체력 계수 = 그 스테이지 시점 공격력(봇 실측)을 다듬은 값, 보상 배율 = 구간별 판당 수입 배율 목표(1~6 ×1.5, 7~11 ×1.35, 12~31 ×1.25, 32~46 ×1.15, 47~50 ×1.12)</t>
         </is>
@@ -1650,9 +1984,19 @@
         <v>150.673</v>
       </c>
       <c r="H30" s="5" t="n"/>
-      <c r="I30" s="5" t="n"/>
-      <c r="J30" s="5" t="n"/>
-      <c r="K30" s="5" t="inlineStr">
+      <c r="I30" s="5" t="inlineStr">
+        <is>
+          <t>Harvest</t>
+        </is>
+      </c>
+      <c r="J30" s="5" t="n">
+        <v>125</v>
+      </c>
+      <c r="K30" s="5" t="n"/>
+      <c r="L30" s="5" t="n"/>
+      <c r="M30" s="5" t="n"/>
+      <c r="N30" s="5" t="n"/>
+      <c r="O30" s="5" t="inlineStr">
         <is>
           <t>2026-10-26 밸런스: 체력 계수 = 그 스테이지 시점 공격력(봇 실측)을 다듬은 값, 보상 배율 = 구간별 판당 수입 배율 목표(1~6 ×1.5, 7~11 ×1.35, 12~31 ×1.25, 32~46 ×1.15, 47~50 ×1.12)</t>
         </is>
@@ -1687,9 +2031,21 @@
         <v>193.53</v>
       </c>
       <c r="H31" s="5" t="n"/>
-      <c r="I31" s="5" t="n"/>
-      <c r="J31" s="5" t="n"/>
-      <c r="K31" s="5" t="inlineStr">
+      <c r="I31" s="5" t="inlineStr">
+        <is>
+          <t>Harvest</t>
+        </is>
+      </c>
+      <c r="J31" s="5" t="n">
+        <v>133</v>
+      </c>
+      <c r="K31" s="5" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="L31" s="5" t="n"/>
+      <c r="M31" s="5" t="n"/>
+      <c r="N31" s="5" t="n"/>
+      <c r="O31" s="5" t="inlineStr">
         <is>
           <t>2026-10-26 밸런스: 체력 계수 = 그 스테이지 시점 공격력(봇 실측)을 다듬은 값, 보상 배율 = 구간별 판당 수입 배율 목표(1~6 ×1.5, 7~11 ×1.35, 12~31 ×1.25, 32~46 ×1.15, 47~50 ×1.12)</t>
         </is>
@@ -1724,9 +2080,21 @@
         <v>231.444</v>
       </c>
       <c r="H32" s="5" t="n"/>
-      <c r="I32" s="5" t="n"/>
-      <c r="J32" s="5" t="n"/>
-      <c r="K32" s="5" t="inlineStr">
+      <c r="I32" s="5" t="inlineStr">
+        <is>
+          <t>Harvest</t>
+        </is>
+      </c>
+      <c r="J32" s="5" t="n">
+        <v>140</v>
+      </c>
+      <c r="K32" s="5" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="L32" s="5" t="n"/>
+      <c r="M32" s="5" t="n"/>
+      <c r="N32" s="5" t="n"/>
+      <c r="O32" s="5" t="inlineStr">
         <is>
           <t>2026-10-26 밸런스: 체력 계수 = 그 스테이지 시점 공격력(봇 실측)을 다듬은 값, 보상 배율 = 구간별 판당 수입 배율 목표(1~6 ×1.5, 7~11 ×1.35, 12~31 ×1.25, 32~46 ×1.15, 47~50 ×1.12)</t>
         </is>
@@ -1765,7 +2133,11 @@
       </c>
       <c r="I33" s="6" t="n"/>
       <c r="J33" s="6" t="n"/>
-      <c r="K33" s="6" t="inlineStr">
+      <c r="K33" s="6" t="n"/>
+      <c r="L33" s="6" t="n"/>
+      <c r="M33" s="6" t="n"/>
+      <c r="N33" s="6" t="n"/>
+      <c r="O33" s="6" t="inlineStr">
         <is>
           <t>2026-10-26 밸런스: 체력 계수 = 그 스테이지 시점 공격력(봇 실측)을 다듬은 값, 보상 배율 = 구간별 판당 수입 배율 목표(1~6 ×1.5, 7~11 ×1.35, 12~31 ×1.25, 32~46 ×1.15, 47~50 ×1.12)</t>
         </is>
@@ -1800,9 +2172,19 @@
         <v>331.006</v>
       </c>
       <c r="H34" s="5" t="n"/>
-      <c r="I34" s="5" t="n"/>
-      <c r="J34" s="5" t="n"/>
-      <c r="K34" s="5" t="inlineStr">
+      <c r="I34" s="5" t="inlineStr">
+        <is>
+          <t>Harvest</t>
+        </is>
+      </c>
+      <c r="J34" s="5" t="n">
+        <v>204</v>
+      </c>
+      <c r="K34" s="5" t="n"/>
+      <c r="L34" s="5" t="n"/>
+      <c r="M34" s="5" t="n"/>
+      <c r="N34" s="5" t="n"/>
+      <c r="O34" s="5" t="inlineStr">
         <is>
           <t>2026-10-26 밸런스: 체력 계수 = 그 스테이지 시점 공격력(봇 실측)을 다듬은 값, 보상 배율 = 구간별 판당 수입 배율 목표(1~6 ×1.5, 7~11 ×1.35, 12~31 ×1.25, 32~46 ×1.15, 47~50 ×1.12)</t>
         </is>
@@ -1837,9 +2219,19 @@
         <v>335.702</v>
       </c>
       <c r="H35" s="5" t="n"/>
-      <c r="I35" s="5" t="n"/>
-      <c r="J35" s="5" t="n"/>
-      <c r="K35" s="5" t="inlineStr">
+      <c r="I35" s="5" t="inlineStr">
+        <is>
+          <t>Harvest</t>
+        </is>
+      </c>
+      <c r="J35" s="5" t="n">
+        <v>196</v>
+      </c>
+      <c r="K35" s="5" t="n"/>
+      <c r="L35" s="5" t="n"/>
+      <c r="M35" s="5" t="n"/>
+      <c r="N35" s="5" t="n"/>
+      <c r="O35" s="5" t="inlineStr">
         <is>
           <t>2026-10-26 밸런스: 체력 계수 = 그 스테이지 시점 공격력(봇 실측)을 다듬은 값, 보상 배율 = 구간별 판당 수입 배율 목표(1~6 ×1.5, 7~11 ×1.35, 12~31 ×1.25, 32~46 ×1.15, 47~50 ×1.12)</t>
         </is>
@@ -1874,9 +2266,19 @@
         <v>340.462</v>
       </c>
       <c r="H36" s="5" t="n"/>
-      <c r="I36" s="5" t="n"/>
-      <c r="J36" s="5" t="n"/>
-      <c r="K36" s="5" t="inlineStr">
+      <c r="I36" s="5" t="inlineStr">
+        <is>
+          <t>Harvest</t>
+        </is>
+      </c>
+      <c r="J36" s="5" t="n">
+        <v>227</v>
+      </c>
+      <c r="K36" s="5" t="n"/>
+      <c r="L36" s="5" t="n"/>
+      <c r="M36" s="5" t="n"/>
+      <c r="N36" s="5" t="n"/>
+      <c r="O36" s="5" t="inlineStr">
         <is>
           <t>2026-10-26 밸런스: 체력 계수 = 그 스테이지 시점 공격력(봇 실측)을 다듬은 값, 보상 배율 = 구간별 판당 수입 배율 목표(1~6 ×1.5, 7~11 ×1.35, 12~31 ×1.25, 32~46 ×1.15, 47~50 ×1.12)</t>
         </is>
@@ -1911,9 +2313,21 @@
         <v>345.289</v>
       </c>
       <c r="H37" s="5" t="n"/>
-      <c r="I37" s="5" t="n"/>
-      <c r="J37" s="5" t="n"/>
-      <c r="K37" s="5" t="inlineStr">
+      <c r="I37" s="5" t="inlineStr">
+        <is>
+          <t>Harvest</t>
+        </is>
+      </c>
+      <c r="J37" s="5" t="n">
+        <v>238</v>
+      </c>
+      <c r="K37" s="5" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="L37" s="5" t="n"/>
+      <c r="M37" s="5" t="n"/>
+      <c r="N37" s="5" t="n"/>
+      <c r="O37" s="5" t="inlineStr">
         <is>
           <t>2026-10-26 밸런스: 체력 계수 = 그 스테이지 시점 공격력(봇 실측)을 다듬은 값, 보상 배율 = 구간별 판당 수입 배율 목표(1~6 ×1.5, 7~11 ×1.35, 12~31 ×1.25, 32~46 ×1.15, 47~50 ×1.12)</t>
         </is>
@@ -1948,9 +2362,23 @@
         <v>350.184</v>
       </c>
       <c r="H38" s="5" t="n"/>
-      <c r="I38" s="5" t="n"/>
-      <c r="J38" s="5" t="n"/>
-      <c r="K38" s="5" t="inlineStr">
+      <c r="I38" s="5" t="inlineStr">
+        <is>
+          <t>Harvest</t>
+        </is>
+      </c>
+      <c r="J38" s="5" t="n">
+        <v>293</v>
+      </c>
+      <c r="K38" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="L38" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="M38" s="5" t="n"/>
+      <c r="N38" s="5" t="n"/>
+      <c r="O38" s="5" t="inlineStr">
         <is>
           <t>2026-10-26 밸런스: 체력 계수 = 그 스테이지 시점 공격력(봇 실측)을 다듬은 값, 보상 배율 = 구간별 판당 수입 배율 목표(1~6 ×1.5, 7~11 ×1.35, 12~31 ×1.25, 32~46 ×1.15, 47~50 ×1.12)</t>
         </is>
@@ -1985,9 +2413,19 @@
         <v>355.152</v>
       </c>
       <c r="H39" s="5" t="n"/>
-      <c r="I39" s="5" t="n"/>
-      <c r="J39" s="5" t="n"/>
-      <c r="K39" s="5" t="inlineStr">
+      <c r="I39" s="5" t="inlineStr">
+        <is>
+          <t>Harvest</t>
+        </is>
+      </c>
+      <c r="J39" s="5" t="n">
+        <v>388</v>
+      </c>
+      <c r="K39" s="5" t="n"/>
+      <c r="L39" s="5" t="n"/>
+      <c r="M39" s="5" t="n"/>
+      <c r="N39" s="5" t="n"/>
+      <c r="O39" s="5" t="inlineStr">
         <is>
           <t>2026-10-26 밸런스: 체력 계수 = 그 스테이지 시점 공격력(봇 실측)을 다듬은 값, 보상 배율 = 구간별 판당 수입 배율 목표(1~6 ×1.5, 7~11 ×1.35, 12~31 ×1.25, 32~46 ×1.15, 47~50 ×1.12)</t>
         </is>
@@ -2022,9 +2460,19 @@
         <v>360.186</v>
       </c>
       <c r="H40" s="5" t="n"/>
-      <c r="I40" s="5" t="n"/>
-      <c r="J40" s="5" t="n"/>
-      <c r="K40" s="5" t="inlineStr">
+      <c r="I40" s="5" t="inlineStr">
+        <is>
+          <t>Harvest</t>
+        </is>
+      </c>
+      <c r="J40" s="5" t="n">
+        <v>344</v>
+      </c>
+      <c r="K40" s="5" t="n"/>
+      <c r="L40" s="5" t="n"/>
+      <c r="M40" s="5" t="n"/>
+      <c r="N40" s="5" t="n"/>
+      <c r="O40" s="5" t="inlineStr">
         <is>
           <t>2026-10-26 밸런스: 체력 계수 = 그 스테이지 시점 공격력(봇 실측)을 다듬은 값, 보상 배율 = 구간별 판당 수입 배율 목표(1~6 ×1.5, 7~11 ×1.35, 12~31 ×1.25, 32~46 ×1.15, 47~50 ×1.12)</t>
         </is>
@@ -2059,9 +2507,21 @@
         <v>365.294</v>
       </c>
       <c r="H41" s="5" t="n"/>
-      <c r="I41" s="5" t="n"/>
-      <c r="J41" s="5" t="n"/>
-      <c r="K41" s="5" t="inlineStr">
+      <c r="I41" s="5" t="inlineStr">
+        <is>
+          <t>Harvest</t>
+        </is>
+      </c>
+      <c r="J41" s="5" t="n">
+        <v>387</v>
+      </c>
+      <c r="K41" s="5" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="L41" s="5" t="n"/>
+      <c r="M41" s="5" t="n"/>
+      <c r="N41" s="5" t="n"/>
+      <c r="O41" s="5" t="inlineStr">
         <is>
           <t>2026-10-26 밸런스: 체력 계수 = 그 스테이지 시점 공격력(봇 실측)을 다듬은 값, 보상 배율 = 구간별 판당 수입 배율 목표(1~6 ×1.5, 7~11 ×1.35, 12~31 ×1.25, 32~46 ×1.15, 47~50 ×1.12)</t>
         </is>
@@ -2096,9 +2556,21 @@
         <v>370.473</v>
       </c>
       <c r="H42" s="5" t="n"/>
-      <c r="I42" s="5" t="n"/>
-      <c r="J42" s="5" t="n"/>
-      <c r="K42" s="5" t="inlineStr">
+      <c r="I42" s="5" t="inlineStr">
+        <is>
+          <t>Harvest</t>
+        </is>
+      </c>
+      <c r="J42" s="5" t="n">
+        <v>391</v>
+      </c>
+      <c r="K42" s="5" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="L42" s="5" t="n"/>
+      <c r="M42" s="5" t="n"/>
+      <c r="N42" s="5" t="n"/>
+      <c r="O42" s="5" t="inlineStr">
         <is>
           <t>2026-10-26 밸런스: 체력 계수 = 그 스테이지 시점 공격력(봇 실측)을 다듬은 값, 보상 배율 = 구간별 판당 수입 배율 목표(1~6 ×1.5, 7~11 ×1.35, 12~31 ×1.25, 32~46 ×1.15, 47~50 ×1.12)</t>
         </is>
@@ -2137,7 +2609,11 @@
       </c>
       <c r="I43" s="6" t="n"/>
       <c r="J43" s="6" t="n"/>
-      <c r="K43" s="6" t="inlineStr">
+      <c r="K43" s="6" t="n"/>
+      <c r="L43" s="6" t="n"/>
+      <c r="M43" s="6" t="n"/>
+      <c r="N43" s="6" t="n"/>
+      <c r="O43" s="6" t="inlineStr">
         <is>
           <t>2026-10-26 밸런스: 체력 계수 = 그 스테이지 시점 공격력(봇 실측)을 다듬은 값, 보상 배율 = 구간별 판당 수입 배율 목표(1~6 ×1.5, 7~11 ×1.35, 12~31 ×1.25, 32~46 ×1.15, 47~50 ×1.12)</t>
         </is>
@@ -2172,9 +2648,19 @@
         <v>413.204</v>
       </c>
       <c r="H44" s="5" t="n"/>
-      <c r="I44" s="5" t="n"/>
-      <c r="J44" s="5" t="n"/>
-      <c r="K44" s="5" t="inlineStr">
+      <c r="I44" s="5" t="inlineStr">
+        <is>
+          <t>Harvest</t>
+        </is>
+      </c>
+      <c r="J44" s="5" t="n">
+        <v>636</v>
+      </c>
+      <c r="K44" s="5" t="n"/>
+      <c r="L44" s="5" t="n"/>
+      <c r="M44" s="5" t="n"/>
+      <c r="N44" s="5" t="n"/>
+      <c r="O44" s="5" t="inlineStr">
         <is>
           <t>2026-10-26 밸런스: 체력 계수 = 그 스테이지 시점 공격력(봇 실측)을 다듬은 값, 보상 배율 = 구간별 판당 수입 배율 목표(1~6 ×1.5, 7~11 ×1.35, 12~31 ×1.25, 32~46 ×1.15, 47~50 ×1.12)</t>
         </is>
@@ -2209,9 +2695,19 @@
         <v>454.455</v>
       </c>
       <c r="H45" s="5" t="n"/>
-      <c r="I45" s="5" t="n"/>
-      <c r="J45" s="5" t="n"/>
-      <c r="K45" s="5" t="inlineStr">
+      <c r="I45" s="5" t="inlineStr">
+        <is>
+          <t>Harvest</t>
+        </is>
+      </c>
+      <c r="J45" s="5" t="n">
+        <v>779</v>
+      </c>
+      <c r="K45" s="5" t="n"/>
+      <c r="L45" s="5" t="n"/>
+      <c r="M45" s="5" t="n"/>
+      <c r="N45" s="5" t="n"/>
+      <c r="O45" s="5" t="inlineStr">
         <is>
           <t>2026-10-26 밸런스: 체력 계수 = 그 스테이지 시점 공격력(봇 실측)을 다듬은 값, 보상 배율 = 구간별 판당 수입 배율 목표(1~6 ×1.5, 7~11 ×1.35, 12~31 ×1.25, 32~46 ×1.15, 47~50 ×1.12)</t>
         </is>
@@ -2246,9 +2742,19 @@
         <v>499.844</v>
       </c>
       <c r="H46" s="5" t="n"/>
-      <c r="I46" s="5" t="n"/>
-      <c r="J46" s="5" t="n"/>
-      <c r="K46" s="5" t="inlineStr">
+      <c r="I46" s="5" t="inlineStr">
+        <is>
+          <t>Harvest</t>
+        </is>
+      </c>
+      <c r="J46" s="5" t="n">
+        <v>886</v>
+      </c>
+      <c r="K46" s="5" t="n"/>
+      <c r="L46" s="5" t="n"/>
+      <c r="M46" s="5" t="n"/>
+      <c r="N46" s="5" t="n"/>
+      <c r="O46" s="5" t="inlineStr">
         <is>
           <t>2026-10-26 밸런스: 체력 계수 = 그 스테이지 시점 공격력(봇 실측)을 다듬은 값, 보상 배율 = 구간별 판당 수입 배율 목표(1~6 ×1.5, 7~11 ×1.35, 12~31 ×1.25, 32~46 ×1.15, 47~50 ×1.12)</t>
         </is>
@@ -2283,9 +2789,21 @@
         <v>549.753</v>
       </c>
       <c r="H47" s="5" t="n"/>
-      <c r="I47" s="5" t="n"/>
-      <c r="J47" s="5" t="n"/>
-      <c r="K47" s="5" t="inlineStr">
+      <c r="I47" s="5" t="inlineStr">
+        <is>
+          <t>Harvest</t>
+        </is>
+      </c>
+      <c r="J47" s="5" t="n">
+        <v>929</v>
+      </c>
+      <c r="K47" s="5" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="L47" s="5" t="n"/>
+      <c r="M47" s="5" t="n"/>
+      <c r="N47" s="5" t="n"/>
+      <c r="O47" s="5" t="inlineStr">
         <is>
           <t>2026-10-26 밸런스: 체력 계수 = 그 스테이지 시점 공격력(봇 실측)을 다듬은 값, 보상 배율 = 구간별 판당 수입 배율 목표(1~6 ×1.5, 7~11 ×1.35, 12~31 ×1.25, 32~46 ×1.15, 47~50 ×1.12)</t>
         </is>
@@ -2320,9 +2838,23 @@
         <v>604.644</v>
       </c>
       <c r="H48" s="5" t="n"/>
-      <c r="I48" s="5" t="n"/>
-      <c r="J48" s="5" t="n"/>
-      <c r="K48" s="5" t="inlineStr">
+      <c r="I48" s="5" t="inlineStr">
+        <is>
+          <t>Harvest</t>
+        </is>
+      </c>
+      <c r="J48" s="5" t="n">
+        <v>902</v>
+      </c>
+      <c r="K48" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="L48" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="M48" s="5" t="n"/>
+      <c r="N48" s="5" t="n"/>
+      <c r="O48" s="5" t="inlineStr">
         <is>
           <t>2026-10-26 밸런스: 체력 계수 = 그 스테이지 시점 공격력(봇 실측)을 다듬은 값, 보상 배율 = 구간별 판당 수입 배율 목표(1~6 ×1.5, 7~11 ×1.35, 12~31 ×1.25, 32~46 ×1.15, 47~50 ×1.12)</t>
         </is>
@@ -2357,9 +2889,19 @@
         <v>613.218</v>
       </c>
       <c r="H49" s="5" t="n"/>
-      <c r="I49" s="5" t="n"/>
-      <c r="J49" s="5" t="n"/>
-      <c r="K49" s="5" t="inlineStr">
+      <c r="I49" s="5" t="inlineStr">
+        <is>
+          <t>Harvest</t>
+        </is>
+      </c>
+      <c r="J49" s="5" t="n">
+        <v>927</v>
+      </c>
+      <c r="K49" s="5" t="n"/>
+      <c r="L49" s="5" t="n"/>
+      <c r="M49" s="5" t="n"/>
+      <c r="N49" s="5" t="n"/>
+      <c r="O49" s="5" t="inlineStr">
         <is>
           <t>2026-10-26 밸런스: 체력 계수 = 그 스테이지 시점 공격력(봇 실측)을 다듬은 값, 보상 배율 = 구간별 판당 수입 배율 목표(1~6 ×1.5, 7~11 ×1.35, 12~31 ×1.25, 32~46 ×1.15, 47~50 ×1.12)</t>
         </is>
@@ -2394,9 +2936,19 @@
         <v>641.8630000000001</v>
       </c>
       <c r="H50" s="5" t="n"/>
-      <c r="I50" s="5" t="n"/>
-      <c r="J50" s="5" t="n"/>
-      <c r="K50" s="5" t="inlineStr">
+      <c r="I50" s="5" t="inlineStr">
+        <is>
+          <t>Harvest</t>
+        </is>
+      </c>
+      <c r="J50" s="5" t="n">
+        <v>924</v>
+      </c>
+      <c r="K50" s="5" t="n"/>
+      <c r="L50" s="5" t="n"/>
+      <c r="M50" s="5" t="n"/>
+      <c r="N50" s="5" t="n"/>
+      <c r="O50" s="5" t="inlineStr">
         <is>
           <t>2026-10-26 밸런스: 체력 계수 = 그 스테이지 시점 공격력(봇 실측)을 다듬은 값, 보상 배율 = 구간별 판당 수입 배율 목표(1~6 ×1.5, 7~11 ×1.35, 12~31 ×1.25, 32~46 ×1.15, 47~50 ×1.12)</t>
         </is>
@@ -2431,9 +2983,21 @@
         <v>671.848</v>
       </c>
       <c r="H51" s="5" t="n"/>
-      <c r="I51" s="5" t="n"/>
-      <c r="J51" s="5" t="n"/>
-      <c r="K51" s="5" t="inlineStr">
+      <c r="I51" s="5" t="inlineStr">
+        <is>
+          <t>Harvest</t>
+        </is>
+      </c>
+      <c r="J51" s="5" t="n">
+        <v>929</v>
+      </c>
+      <c r="K51" s="5" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="L51" s="5" t="n"/>
+      <c r="M51" s="5" t="n"/>
+      <c r="N51" s="5" t="n"/>
+      <c r="O51" s="5" t="inlineStr">
         <is>
           <t>2026-10-26 밸런스: 체력 계수 = 그 스테이지 시점 공격력(봇 실측)을 다듬은 값, 보상 배율 = 구간별 판당 수입 배율 목표(1~6 ×1.5, 7~11 ×1.35, 12~31 ×1.25, 32~46 ×1.15, 47~50 ×1.12)</t>
         </is>
@@ -2468,9 +3032,21 @@
         <v>703.234</v>
       </c>
       <c r="H52" s="5" t="n"/>
-      <c r="I52" s="5" t="n"/>
-      <c r="J52" s="5" t="n"/>
-      <c r="K52" s="5" t="inlineStr">
+      <c r="I52" s="5" t="inlineStr">
+        <is>
+          <t>Harvest</t>
+        </is>
+      </c>
+      <c r="J52" s="5" t="n">
+        <v>928</v>
+      </c>
+      <c r="K52" s="5" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="L52" s="5" t="n"/>
+      <c r="M52" s="5" t="n"/>
+      <c r="N52" s="5" t="n"/>
+      <c r="O52" s="5" t="inlineStr">
         <is>
           <t>2026-10-26 밸런스: 체력 계수 = 그 스테이지 시점 공격력(봇 실측)을 다듬은 값, 보상 배율 = 구간별 판당 수입 배율 목표(1~6 ×1.5, 7~11 ×1.35, 12~31 ×1.25, 32~46 ×1.15, 47~50 ×1.12)</t>
         </is>
@@ -2509,7 +3085,11 @@
       </c>
       <c r="I53" s="6" t="n"/>
       <c r="J53" s="6" t="n"/>
-      <c r="K53" s="6" t="inlineStr">
+      <c r="K53" s="6" t="n"/>
+      <c r="L53" s="6" t="n"/>
+      <c r="M53" s="6" t="n"/>
+      <c r="N53" s="6" t="n"/>
+      <c r="O53" s="6" t="inlineStr">
         <is>
           <t>2026-10-26 밸런스: 체력 계수 = 그 스테이지 시점 공격력(봇 실측)을 다듬은 값, 보상 배율 = 구간별 판당 수입 배율 목표(1~6 ×1.5, 7~11 ×1.35, 12~31 ×1.25, 32~46 ×1.15, 47~50 ×1.12)</t>
         </is>
